--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118258395</v>
+        <v>118258924</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -710,29 +710,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västerins (Västerins), Vstm</t>
+          <t>Överstmossen (Överstmossen), Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588798</v>
+        <v>588525</v>
       </c>
       <c r="R2" t="n">
-        <v>6634600</v>
+        <v>6634559</v>
       </c>
       <c r="S2" t="n">
         <v>7</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -942,7 +942,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118258064</v>
+        <v>118258395</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -977,17 +977,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588901</v>
+        <v>588798</v>
       </c>
       <c r="R4" t="n">
-        <v>6634502</v>
+        <v>6634600</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,22 +1053,37 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118258924</v>
+        <v>118258064</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1103,7 +1118,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1118,17 +1133,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Överstmossen (Överstmossen), Vstm</t>
+          <t>Västerins (Västerins), Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588525</v>
+        <v>588901</v>
       </c>
       <c r="R5" t="n">
-        <v>6634559</v>
+        <v>6634502</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1157,7 +1172,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1167,7 +1182,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,30 +1194,15 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>121263118</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>121263083</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121263118</v>
+        <v>121263083</v>
       </c>
       <c r="B6" t="n">
         <v>98081</v>
@@ -1244,31 +1244,31 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Överstmossen 2 (knärot), Vstm</t>
+          <t>Västerins 5 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588525</v>
+        <v>588797</v>
       </c>
       <c r="R6" t="n">
-        <v>6634558</v>
+        <v>6634601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>U-Sal-1072</t>
+          <t>U-Sal-1070</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121263083</v>
+        <v>121263118</v>
       </c>
       <c r="B7" t="n">
         <v>98081</v>
@@ -1382,31 +1382,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västerins 5 (knärot), Vstm</t>
+          <t>Överstmossen 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588797</v>
+        <v>588525</v>
       </c>
       <c r="R7" t="n">
-        <v>6634601</v>
+        <v>6634558</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>U-Sal-1070</t>
+          <t>U-Sal-1072</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121263083</v>
+        <v>121263118</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1244,31 +1244,31 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västerins 5 (knärot), Vstm</t>
+          <t>Överstmossen 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588797</v>
+        <v>588525</v>
       </c>
       <c r="R6" t="n">
-        <v>6634601</v>
+        <v>6634558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>U-Sal-1070</t>
+          <t>U-Sal-1072</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121263118</v>
+        <v>121263083</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1382,31 +1382,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Överstmossen 2 (knärot), Vstm</t>
+          <t>Västerins 5 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588525</v>
+        <v>588797</v>
       </c>
       <c r="R7" t="n">
-        <v>6634558</v>
+        <v>6634601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>U-Sal-1072</t>
+          <t>U-Sal-1070</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>121263118</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>121263083</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>121263118</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>121263083</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121263118</v>
+        <v>121263083</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1244,31 +1244,31 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Överstmossen 2 (knärot), Vstm</t>
+          <t>Västerins 5 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588525</v>
+        <v>588797</v>
       </c>
       <c r="R6" t="n">
-        <v>6634558</v>
+        <v>6634601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>U-Sal-1072</t>
+          <t>U-Sal-1070</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121263083</v>
+        <v>121263118</v>
       </c>
       <c r="B7" t="n">
         <v>98098</v>
@@ -1382,31 +1382,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västerins 5 (knärot), Vstm</t>
+          <t>Överstmossen 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588797</v>
+        <v>588525</v>
       </c>
       <c r="R7" t="n">
-        <v>6634601</v>
+        <v>6634558</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>U-Sal-1070</t>
+          <t>U-Sal-1072</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>121263083</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>121263118</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>121263083</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>121263118</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121263083</v>
+        <v>121263118</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1244,31 +1244,31 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västerins 5 (knärot), Vstm</t>
+          <t>Överstmossen 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588797</v>
+        <v>588525</v>
       </c>
       <c r="R6" t="n">
-        <v>6634601</v>
+        <v>6634558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>U-Sal-1070</t>
+          <t>U-Sal-1072</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121263118</v>
+        <v>121263083</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1382,31 +1382,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Överstmossen 2 (knärot), Vstm</t>
+          <t>Västerins 5 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588525</v>
+        <v>588797</v>
       </c>
       <c r="R7" t="n">
-        <v>6634558</v>
+        <v>6634601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>U-Sal-1072</t>
+          <t>U-Sal-1070</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118258924</v>
+        <v>118258064</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -725,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Överstmossen (Överstmossen), Vstm</t>
+          <t>Västerins, Västerins, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588525</v>
+        <v>588901</v>
       </c>
       <c r="R2" t="n">
-        <v>6634559</v>
+        <v>6634502</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,31 +780,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -819,12 +799,7 @@
         <v>118258332</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -866,7 +841,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västerins (Västerins), Vstm</t>
+          <t>Västerins, Västerins, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -945,12 +920,7 @@
         <v>118258395</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +962,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västerins (Västerins), Vstm</t>
+          <t>Västerins, Västerins, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1083,15 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118258064</v>
+        <v>118258924</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1083,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1133,17 +1098,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västerins (Västerins), Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588901</v>
+        <v>588525</v>
       </c>
       <c r="R5" t="n">
-        <v>6634502</v>
+        <v>6634559</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1172,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1182,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1193,31 +1158,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121263118</v>
+        <v>121263083</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,31 +1219,31 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Överstmossen 2 (knärot), Vstm</t>
+          <t>Västerins 5 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588525</v>
+        <v>588797</v>
       </c>
       <c r="R6" t="n">
-        <v>6634558</v>
+        <v>6634601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1295,7 +1270,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>U-Sal-1072</t>
+          <t>U-Sal-1070</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1347,15 +1322,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121263083</v>
+        <v>121263118</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,31 +1352,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västerins 5 (knärot), Vstm</t>
+          <t>Överstmossen (knärot2), Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588797</v>
+        <v>588525</v>
       </c>
       <c r="R7" t="n">
-        <v>6634601</v>
+        <v>6634558</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1433,7 +1403,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>U-Sal-1070</t>
+          <t>U-Sal-1072</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 55550-2023 artfynd.xlsx
+++ b/artfynd/A 55550-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118258064</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118258332</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118258395</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1186,6 +1206,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118258924</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1319,6 +1344,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121263083</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1452,8 +1482,21 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121263118</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>